--- a/output/pdf_financials_xlsx/ENRG.xlsx
+++ b/output/pdf_financials_xlsx/ENRG.xlsx
@@ -3791,28 +3791,28 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.107729</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.507429</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.507429</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.507429</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.507429</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.276632</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.223662</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.116534</v>
       </c>
     </row>
     <row r="93">
@@ -4762,7 +4762,7 @@
         <v>0.5911</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.8526</v>
+        <v>0.856935</v>
       </c>
       <c r="J118" s="3" t="n">
         <v>0.2065</v>
@@ -6143,7 +6143,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>-</t>
@@ -6682,7 +6686,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -7111,7 +7119,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -8738,7 +8750,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E55" t="inlineStr">
         <is>
           <t>-</t>
@@ -9358,7 +9374,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -9606,7 +9626,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -9972,7 +9996,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" t="inlineStr">
         <is>
           <t>-</t>
@@ -10340,7 +10368,11 @@
           <t>Options issued for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/ENRG.xlsx
+++ b/output/pdf_financials_xlsx/ENRG.xlsx
@@ -1732,31 +1732,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.389802</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.239733</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.358236</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.101392</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.072695</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.004898</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.395118</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.07011299999999999</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.013709</v>
       </c>
     </row>
     <row r="35">
@@ -1800,31 +1800,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.389802</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.239733</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.358236</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.004</v>
+        <v>0.105392</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.0175</v>
+        <v>0.090195</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>-0.00374</v>
+        <v>0.001158</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.395118</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.07011299999999999</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.013709</v>
       </c>
     </row>
     <row r="37">
@@ -2208,31 +2208,31 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.389802</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.427766</v>
+        <v>0.188033</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.364361</v>
+        <v>0.006125</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.847751</v>
+        <v>0.746359</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.144691</v>
+        <v>0.071996</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.008638</v>
+        <v>0.00374</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.525261</v>
+        <v>0.130143</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.08948299999999999</v>
+        <v>0.01937</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.039441</v>
+        <v>0.025732</v>
       </c>
     </row>
     <row r="49">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8323,7 +8323,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
